--- a/data/trans_orig/IMC_inf_MED_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R2-Habitat-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>57550</v>
+        <v>68862</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>48699</v>
+        <v>59050</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>66002</v>
+        <v>78454</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5642354894405667</v>
+        <v>0.5427192255996899</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4774639284488597</v>
+        <v>0.465385153799679</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6471070646694022</v>
+        <v>0.6183138921476233</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>44267</v>
+        <v>55560</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>35862</v>
+        <v>46004</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>52452</v>
+        <v>64576</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4681022004524167</v>
+        <v>0.4623159654674296</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.379230903427722</v>
+        <v>0.3828044347696301</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5546644508492008</v>
+        <v>0.5373410447456504</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>101816</v>
+        <v>124422</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>89532</v>
+        <v>111100</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>113389</v>
+        <v>137054</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.5179858155758553</v>
+        <v>0.5036088299743885</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.4554889697379699</v>
+        <v>0.4496872096854159</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5768587052022045</v>
+        <v>0.5547394651770179</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>44446</v>
+        <v>58022</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>35994</v>
+        <v>48430</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>53297</v>
+        <v>67834</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4357645105594333</v>
+        <v>0.4572807744003101</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3528929353305978</v>
+        <v>0.3816861078523767</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5225360715511403</v>
+        <v>0.534614846200321</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>50299</v>
+        <v>64617</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>42114</v>
+        <v>55601</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>58704</v>
+        <v>74173</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5318977995475833</v>
+        <v>0.5376840345325704</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4453355491507994</v>
+        <v>0.4626589552543497</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6207690965722779</v>
+        <v>0.6171955652303699</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>94746</v>
+        <v>122639</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>83173</v>
+        <v>110007</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>107030</v>
+        <v>135961</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4820141844241447</v>
+        <v>0.4963911700256115</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4231412947977954</v>
+        <v>0.4452605348229818</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5445110302620303</v>
+        <v>0.550312790314584</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>91085</v>
+        <v>103516</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>80918</v>
+        <v>91925</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>101333</v>
+        <v>114061</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5785991126215978</v>
+        <v>0.5438607176460495</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.5140176965676876</v>
+        <v>0.482966425929688</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.6436968969646361</v>
+        <v>0.5992621147474041</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>60637</v>
+        <v>75021</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>51103</v>
+        <v>63897</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>70086</v>
+        <v>85336</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4206671713042348</v>
+        <v>0.4207535104855215</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3545234296905573</v>
+        <v>0.3583649440951766</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4862216598586231</v>
+        <v>0.4786045163538551</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>151722</v>
+        <v>178537</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>137451</v>
+        <v>163134</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>165039</v>
+        <v>193623</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.503110123184315</v>
+        <v>0.4843165928103053</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4557873569854096</v>
+        <v>0.442535183409052</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5472704475085833</v>
+        <v>0.5252425255191616</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>66338</v>
+        <v>86819</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>56090</v>
+        <v>76274</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>76505</v>
+        <v>98410</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4214008873784021</v>
+        <v>0.4561392823539505</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3563031030353639</v>
+        <v>0.4007378852525958</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.4859823034323125</v>
+        <v>0.5170335740703119</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>83508</v>
+        <v>103280</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>74059</v>
+        <v>92965</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>93042</v>
+        <v>114404</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5793328286957652</v>
+        <v>0.5792464895144785</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5137783401413769</v>
+        <v>0.5213954836461449</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.6454765703094427</v>
+        <v>0.6416350559048234</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>149846</v>
+        <v>190099</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>136529</v>
+        <v>175013</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>164117</v>
+        <v>205502</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.496889876815685</v>
+        <v>0.5156834071896947</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.4527295524914167</v>
+        <v>0.4747574744808384</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.5442126430145904</v>
+        <v>0.557464816590948</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>449</v>
+        <v>551</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>57131</v>
+        <v>67973</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>47507</v>
+        <v>58561</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>64957</v>
+        <v>77171</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4952889776515371</v>
+        <v>0.4947234388206549</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4118581917373507</v>
+        <v>0.4262207806638624</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5631372324399387</v>
+        <v>0.5616735620276118</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>50871</v>
+        <v>58943</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>43383</v>
+        <v>49888</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>60279</v>
+        <v>68127</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4436321400984123</v>
+        <v>0.4523679302265973</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3783306690345282</v>
+        <v>0.3828721900940474</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.5256764872024023</v>
+        <v>0.5228492555045956</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>108002</v>
+        <v>126916</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>95153</v>
+        <v>114912</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>118847</v>
+        <v>139736</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.469536739311463</v>
+        <v>0.474107076536109</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.4136761941727872</v>
+        <v>0.4292675729676123</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.516681459073279</v>
+        <v>0.5220007047947243</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>58218</v>
+        <v>69422</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>50392</v>
+        <v>60224</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>67842</v>
+        <v>78834</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.504711022348463</v>
+        <v>0.5052765611793451</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.4368627675600613</v>
+        <v>0.4383264379723881</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.5881418082626493</v>
+        <v>0.5737792193361375</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>63799</v>
+        <v>71356</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>54391</v>
+        <v>62172</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>71287</v>
+        <v>80411</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5563678599015877</v>
+        <v>0.5476320697734027</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.474323512797598</v>
+        <v>0.4771507444954044</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6216693309654719</v>
+        <v>0.6171278099059526</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>122017</v>
+        <v>140778</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>111172</v>
+        <v>127958</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>134866</v>
+        <v>152782</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.530463260688537</v>
+        <v>0.5258929234638909</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.4833185409267209</v>
+        <v>0.4779992952052757</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.5863238058272127</v>
+        <v>0.5707324270323876</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>75151</v>
+        <v>84729</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>65443</v>
+        <v>72790</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>85133</v>
+        <v>94943</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.506180911917138</v>
+        <v>0.4947607730123137</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4407954250045588</v>
+        <v>0.4250477604446222</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5734192878880243</v>
+        <v>0.5544041473364365</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>69739</v>
+        <v>77628</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>59390</v>
+        <v>66906</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>80567</v>
+        <v>89464</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4734852736076617</v>
+        <v>0.4636962808917721</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.403221344996112</v>
+        <v>0.3996516047556662</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5470001389401767</v>
+        <v>0.5343995783016569</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>144889</v>
+        <v>162357</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>130385</v>
+        <v>145093</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>159712</v>
+        <v>178235</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4898981383554949</v>
+        <v>0.4794047043214177</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4408548113168896</v>
+        <v>0.428429902623998</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5400150810799182</v>
+        <v>0.5262902104205455</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>73315</v>
+        <v>86523</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>63333</v>
+        <v>76309</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>83023</v>
+        <v>98462</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.493819088082862</v>
+        <v>0.5052392269876863</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4265807121119756</v>
+        <v>0.4455958526635637</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.5592045749954411</v>
+        <v>0.5749522395553782</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>77550</v>
+        <v>89783</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>66722</v>
+        <v>77947</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>87899</v>
+        <v>100505</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5265147263923382</v>
+        <v>0.5363037191082279</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.4529998610598233</v>
+        <v>0.4656004216983433</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.596778655003888</v>
+        <v>0.6003483952443337</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>150865</v>
+        <v>176306</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>136042</v>
+        <v>160428</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>165369</v>
+        <v>193570</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5101018616445051</v>
+        <v>0.5205952956785823</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4599849189200818</v>
+        <v>0.4737097895794546</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.5591451886831104</v>
+        <v>0.571570097376002</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>262560</v>
+        <v>303500</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>301398</v>
+        <v>345372</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.5368847747166713</v>
+        <v>0.5194073618784171</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.5018018298204001</v>
+        <v>0.4849276368679208</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5760283859890361</v>
+        <v>0.5518300341758322</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>506430</v>
+        <v>592231</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>481200</v>
+        <v>564377</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>532083</v>
+        <v>621068</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4946073589230291</v>
+        <v>0.4846192482017541</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.4699657488694993</v>
+        <v>0.4618263964367272</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.5196611328841555</v>
+        <v>0.5082161603494973</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>349</v>
+        <v>434</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>242318</v>
+        <v>300787</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>221836</v>
+        <v>280494</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>260674</v>
+        <v>322366</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4631152252833288</v>
+        <v>0.4805926381215829</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.423971614010964</v>
+        <v>0.448169965824168</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4981981701795999</v>
+        <v>0.5150723631320794</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>396</v>
+        <v>473</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>275156</v>
+        <v>329037</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>256569</v>
+        <v>308902</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>293350</v>
+        <v>349592</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.5495753939059956</v>
+        <v>0.5519006187905663</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.5124510828227896</v>
+        <v>0.5181286473350197</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.5859139402897362</v>
+        <v>0.5863781379423997</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>745</v>
+        <v>907</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>517474</v>
+        <v>629823</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>491821</v>
+        <v>600986</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>542704</v>
+        <v>657677</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5053926410769709</v>
+        <v>0.5153807517982459</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.4803388671158446</v>
+        <v>0.4917838396505027</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.5300342511305007</v>
+        <v>0.5381736035632728</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>50589</v>
+        <v>61044</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>41700</v>
+        <v>51476</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>58729</v>
+        <v>70842</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5152621621131193</v>
+        <v>0.5026489801925585</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.424724326505665</v>
+        <v>0.4238659841241574</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.598171113126971</v>
+        <v>0.58332205702336</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>36324</v>
+        <v>41506</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>29716</v>
+        <v>33342</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>44556</v>
+        <v>50280</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4176797604816704</v>
+        <v>0.3854322925223158</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.3416969920382628</v>
+        <v>0.309619982408513</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5123330209094932</v>
+        <v>0.4669046376627817</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>86913</v>
+        <v>102550</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>75380</v>
+        <v>89457</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>98533</v>
+        <v>116173</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4694261581591092</v>
+        <v>0.4475597274491805</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.4071359294981607</v>
+        <v>0.3904181486342744</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5321855371770005</v>
+        <v>0.5070122955924925</v>
       </c>
     </row>
     <row r="5">
@@ -2117,67 +2117,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>47592</v>
+        <v>60401</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>39452</v>
+        <v>50603</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>56481</v>
+        <v>69969</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4847378378868807</v>
+        <v>0.4973510198074414</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.401828886873029</v>
+        <v>0.41667794297664</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5752756734943351</v>
+        <v>0.5761340158758423</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>50643</v>
+        <v>66181</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>42411</v>
+        <v>57407</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>57251</v>
+        <v>74345</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5823202395183296</v>
+        <v>0.6145677074776843</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4876669790905068</v>
+        <v>0.5330953623372183</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.6583030079617371</v>
+        <v>0.6903800175914869</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>98235</v>
+        <v>126582</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>86615</v>
+        <v>112959</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>109768</v>
+        <v>139675</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5305738418408908</v>
+        <v>0.5524402725508194</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4678144628229997</v>
+        <v>0.4929877044075071</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5928640705018393</v>
+        <v>0.6095818513657254</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2230,16 +2230,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2263,67 +2263,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71274</v>
+        <v>82422</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>61748</v>
+        <v>71841</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>81372</v>
+        <v>93876</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4616196022370728</v>
+        <v>0.4509062305038418</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3999239181675459</v>
+        <v>0.3930206337094511</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5270175682148951</v>
+        <v>0.513570108734688</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>39962</v>
+        <v>45250</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>32035</v>
+        <v>36270</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>48350</v>
+        <v>54559</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2712067021464331</v>
+        <v>0.2648098233413929</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2174129464237343</v>
+        <v>0.2122583406619638</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3281362821841821</v>
+        <v>0.3192929288157726</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>111236</v>
+        <v>127671</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>97568</v>
+        <v>112587</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>124168</v>
+        <v>141657</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3686382099786661</v>
+        <v>0.3609928791853461</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3233418141967616</v>
+        <v>0.3183411114489273</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4114929070542947</v>
+        <v>0.4005382807953222</v>
       </c>
     </row>
     <row r="8">
@@ -2334,67 +2334,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>83126</v>
+        <v>100369</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>73028</v>
+        <v>88915</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>92652</v>
+        <v>110950</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5383803977629271</v>
+        <v>0.5490937694961582</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4729824317851049</v>
+        <v>0.4864298912653121</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.6000760818324541</v>
+        <v>0.6069793662905489</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>107386</v>
+        <v>125626</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>98998</v>
+        <v>116317</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>115313</v>
+        <v>134606</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7287932978535668</v>
+        <v>0.7351901766586071</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.671863717815818</v>
+        <v>0.6807070711842272</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.7825870535762658</v>
+        <v>0.7877416593380361</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>291</v>
+        <v>346</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>190513</v>
+        <v>225996</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>177581</v>
+        <v>212010</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>204181</v>
+        <v>241080</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6313617900213339</v>
+        <v>0.6390071208146538</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5885070929457052</v>
+        <v>0.5994617192046779</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6766581858032384</v>
+        <v>0.6816588885510729</v>
       </c>
     </row>
     <row r="9">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2426,16 +2426,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2480,67 +2480,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>42253</v>
+        <v>56136</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>33369</v>
+        <v>45796</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>51368</v>
+        <v>66632</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3540703285341519</v>
+        <v>0.3812960492956445</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2796236388571795</v>
+        <v>0.311065543538451</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.430452015724017</v>
+        <v>0.4525889358928012</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>37839</v>
+        <v>48082</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>30815</v>
+        <v>39479</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>45822</v>
+        <v>56074</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.339452758575235</v>
+        <v>0.3608778813524168</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2764397319623148</v>
+        <v>0.2963065502715634</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4110662016717099</v>
+        <v>0.4208632125678268</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>80093</v>
+        <v>104218</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>68094</v>
+        <v>92207</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>91039</v>
+        <v>117840</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.347010536761592</v>
+        <v>0.3715961554332918</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2950241346990489</v>
+        <v>0.3287715072784502</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3944364529421863</v>
+        <v>0.4201686174926065</v>
       </c>
     </row>
     <row r="11">
@@ -2551,67 +2551,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>77083</v>
+        <v>91088</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67968</v>
+        <v>80592</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>85967</v>
+        <v>101428</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.6459296714658481</v>
+        <v>0.6187039507043555</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.569547984275983</v>
+        <v>0.5474110641071988</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.7203763611428203</v>
+        <v>0.6889344564615494</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>73633</v>
+        <v>85154</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>65650</v>
+        <v>77162</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>80657</v>
+        <v>93757</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.660547241424765</v>
+        <v>0.6391221186475832</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.588933798328291</v>
+        <v>0.5791367874321732</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7235602680376854</v>
+        <v>0.7036934497284366</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>150715</v>
+        <v>176242</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>139769</v>
+        <v>162620</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>162714</v>
+        <v>188253</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.652989463238408</v>
+        <v>0.6284038445667082</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.6055635470578137</v>
+        <v>0.5798313825073932</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7049758653009512</v>
+        <v>0.6712284927215497</v>
       </c>
     </row>
     <row r="12">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2643,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2664,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>73684</v>
+        <v>84459</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63565</v>
+        <v>73080</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>84391</v>
+        <v>95118</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4837974890422837</v>
+        <v>0.4691114929937021</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4173550465710502</v>
+        <v>0.4059116241574704</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5540934467871534</v>
+        <v>0.5283141591299778</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>55360</v>
+        <v>62091</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>45913</v>
+        <v>51248</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>65961</v>
+        <v>72877</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3914840327259841</v>
+        <v>0.3747330004568365</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3246744041987293</v>
+        <v>0.3092929776337591</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4664484701901231</v>
+        <v>0.4398313399712539</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>129045</v>
+        <v>146550</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>115569</v>
+        <v>129898</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>144050</v>
+        <v>161137</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4393525234287259</v>
+        <v>0.4238804015120362</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3934722225712896</v>
+        <v>0.3757168922230515</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4904413911930637</v>
+        <v>0.4660732637323636</v>
       </c>
     </row>
     <row r="14">
@@ -2768,67 +2768,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>78620</v>
+        <v>95581</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>67913</v>
+        <v>84922</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>88739</v>
+        <v>106960</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5162025109577163</v>
+        <v>0.5308885070062979</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4459065532128466</v>
+        <v>0.4716858408700221</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.5826449534289497</v>
+        <v>0.5940883758425295</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>86051</v>
+        <v>103603</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>75450</v>
+        <v>92817</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>95498</v>
+        <v>114446</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6085159672740159</v>
+        <v>0.6252669995431634</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5335515298098767</v>
+        <v>0.5601686600287468</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6753255958012707</v>
+        <v>0.690707022366241</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>164671</v>
+        <v>199184</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>149666</v>
+        <v>184597</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>178147</v>
+        <v>215836</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5606474765712741</v>
+        <v>0.5761195984879638</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.5095586088069364</v>
+        <v>0.5339267362676363</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6065277774287107</v>
+        <v>0.6242831077769484</v>
       </c>
     </row>
     <row r="15">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2860,16 +2860,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>403</v>
+        <v>477</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
     </row>
     <row r="17">
@@ -2985,67 +2985,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>286420</v>
+        <v>347439</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>267514</v>
+        <v>327524</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>304521</v>
+        <v>369171</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5463731495178916</v>
+        <v>0.5501812322109428</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.510307255451978</v>
+        <v>0.5186443961482414</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5809015748057479</v>
+        <v>0.5845941408716442</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>474</v>
+        <v>569</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>317713</v>
+        <v>380564</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>301865</v>
+        <v>362632</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>334461</v>
+        <v>398720</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.6521214086158018</v>
+        <v>0.6589939323793537</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6195931041514716</v>
+        <v>0.6279420322653032</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.6864980051607779</v>
+        <v>0.6904332480665573</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>881</v>
+        <v>1062</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>604134</v>
+        <v>728004</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>577823</v>
+        <v>701583</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>630434</v>
+        <v>756885</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.5973118750184674</v>
+        <v>0.6021571441599545</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.5712979247049845</v>
+        <v>0.5803038512594035</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6233149445503311</v>
+        <v>0.626045914808942</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3363,67 +3363,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>26396</v>
+        <v>29685</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>20031</v>
+        <v>22259</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>32644</v>
+        <v>36207</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.487549269546196</v>
+        <v>0.5057161299999388</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3699802851510691</v>
+        <v>0.3792054019609104</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6029422535339203</v>
+        <v>0.6168325764837642</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>12575</v>
+        <v>13964</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>8773</v>
+        <v>9783</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>17121</v>
+        <v>18883</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3079033250234208</v>
+        <v>0.3197592929027244</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2148196034587746</v>
+        <v>0.2240360936076402</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4192190353324493</v>
+        <v>0.4324158400784119</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>38972</v>
+        <v>43649</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>30650</v>
+        <v>34493</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>47651</v>
+        <v>51580</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.4103041980312206</v>
+        <v>0.4263890309916499</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.3226951955440261</v>
+        <v>0.3369495527378939</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5016818797649154</v>
+        <v>0.5038698989820064</v>
       </c>
     </row>
     <row r="5">
@@ -3434,67 +3434,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>27745</v>
+        <v>29014</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21497</v>
+        <v>22492</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>34110</v>
+        <v>36440</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.512450730453804</v>
+        <v>0.4942838700000611</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3970577464660796</v>
+        <v>0.3831674235162358</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6300197148489315</v>
+        <v>0.6207945980390897</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>28266</v>
+        <v>29705</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>23720</v>
+        <v>24786</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>32068</v>
+        <v>33886</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6920966749765792</v>
+        <v>0.6802407070972757</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5807809646675506</v>
+        <v>0.5675841599215881</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.7851803965412254</v>
+        <v>0.7759639063923598</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>56010</v>
+        <v>58719</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>47331</v>
+        <v>50788</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>64332</v>
+        <v>67875</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.5896958019687795</v>
+        <v>0.5736109690083501</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4983181202350841</v>
+        <v>0.4961301010179937</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.6773048044559739</v>
+        <v>0.6630504472621059</v>
       </c>
     </row>
     <row r="6">
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -3526,16 +3526,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3547,16 +3547,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3580,67 +3580,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>50647</v>
+        <v>51207</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>41339</v>
+        <v>41955</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>60934</v>
+        <v>61667</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4870690894429632</v>
+        <v>0.4736241316618846</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3975581550541585</v>
+        <v>0.38804888292108</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5860030008421452</v>
+        <v>0.5703711118317061</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>19100</v>
+        <v>20106</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>13454</v>
+        <v>14279</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>25143</v>
+        <v>26452</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2831268183703031</v>
+        <v>0.2871755741948049</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1994270259844007</v>
+        <v>0.203944336157051</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3727088091518325</v>
+        <v>0.3778254799453182</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>69747</v>
+        <v>71312</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>58413</v>
+        <v>59657</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>82426</v>
+        <v>84832</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4068206213874858</v>
+        <v>0.4003421286420213</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3407109677984132</v>
+        <v>0.3349111151188362</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4807702562321058</v>
+        <v>0.4762401344428136</v>
       </c>
     </row>
     <row r="8">
@@ -3651,67 +3651,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>53336</v>
+        <v>56910</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>43049</v>
+        <v>46450</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>62644</v>
+        <v>66162</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5129309105570368</v>
+        <v>0.5263758683381153</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.413996999157855</v>
+        <v>0.429628888168294</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.6024418449458417</v>
+        <v>0.6119511170789197</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>48361</v>
+        <v>49906</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>42318</v>
+        <v>43560</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>54007</v>
+        <v>55733</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7168731816296969</v>
+        <v>0.7128244258051951</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6272911908481675</v>
+        <v>0.622174520054682</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8005729740155991</v>
+        <v>0.7960556638429492</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>101698</v>
+        <v>106816</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>89019</v>
+        <v>93296</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>113032</v>
+        <v>118471</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.5931793786125141</v>
+        <v>0.5996578713579785</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5192297437678941</v>
+        <v>0.523759865557186</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6592890322015867</v>
+        <v>0.6650888848811637</v>
       </c>
     </row>
     <row r="9">
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3764,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3803,61 +3803,61 @@
         <v>22948</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>16111</v>
+        <v>16418</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>29863</v>
+        <v>30275</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3283217737813646</v>
+        <v>0.3238200387066683</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2305122247356108</v>
+        <v>0.231670074384504</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4272663074512655</v>
+        <v>0.4272092514734365</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>15293</v>
+        <v>16854</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>10308</v>
+        <v>11940</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>21938</v>
+        <v>23178</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2772141845624366</v>
+        <v>0.2897581056541405</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1868484252775325</v>
+        <v>0.2052688481673331</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.397663682157914</v>
+        <v>0.3984839817156577</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>38241</v>
+        <v>39802</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>30119</v>
+        <v>31082</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>48987</v>
+        <v>49352</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3057771848893341</v>
+        <v>0.3084653262555729</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2408351725317009</v>
+        <v>0.2408888403283878</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3917082930497531</v>
+        <v>0.382481121449293</v>
       </c>
     </row>
     <row r="11">
@@ -3868,67 +3868,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>46946</v>
+        <v>47918</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>40031</v>
+        <v>40591</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>53783</v>
+        <v>54448</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.6716782262186355</v>
+        <v>0.6761799612933317</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.5727336925487344</v>
+        <v>0.5727907485265634</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.7694877752643892</v>
+        <v>0.768329925615496</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>39874</v>
+        <v>41312</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>33229</v>
+        <v>34988</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>44859</v>
+        <v>46226</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7227858154375636</v>
+        <v>0.7102418943458596</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6023363178420872</v>
+        <v>0.6015160182843423</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8131515747224677</v>
+        <v>0.7947311518326668</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>86820</v>
+        <v>89230</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>76074</v>
+        <v>79680</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>94942</v>
+        <v>97950</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6942228151106661</v>
+        <v>0.691534673744427</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.608291706950247</v>
+        <v>0.6175188785507069</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7591648274682994</v>
+        <v>0.7591111596716121</v>
       </c>
     </row>
     <row r="12">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3960,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4014,67 +4014,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>23444</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>16842</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>30639</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3245271086390318</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2331286520589333</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4241199451606051</v>
+      </c>
+      <c r="J13" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>21347</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>15295</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>28828</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>0.3172097272846455</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0.2272830970844102</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0.4283762061898322</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>27</v>
-      </c>
       <c r="K13" s="5" t="n">
-        <v>19112</v>
+        <v>20557</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>13283</v>
+        <v>14647</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>25460</v>
+        <v>27318</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2627108838418433</v>
+        <v>0.2676923221742017</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1825840409797334</v>
+        <v>0.1907242666561637</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3499589681711626</v>
+        <v>0.3557229335302955</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>40459</v>
+        <v>44002</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>31363</v>
+        <v>34838</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>50234</v>
+        <v>53730</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2888991269084244</v>
+        <v>0.2952415102508054</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.223946147936064</v>
+        <v>0.2337515672892923</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3586941953831799</v>
+        <v>0.3605161656256465</v>
       </c>
     </row>
     <row r="14">
@@ -4085,67 +4085,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>45949</v>
+        <v>48798</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>38468</v>
+        <v>41603</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>52001</v>
+        <v>55400</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.6827902727153546</v>
+        <v>0.6754728913609681</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5716237938101675</v>
+        <v>0.5758800548393948</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.7727169029155898</v>
+        <v>0.7668713479410666</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>53638</v>
+        <v>56238</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>47290</v>
+        <v>49477</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>59467</v>
+        <v>62148</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7372891161581567</v>
+        <v>0.7323076778257982</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6500410318288375</v>
+        <v>0.6442770664697044</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8174159590202665</v>
+        <v>0.8092757333438365</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>99587</v>
+        <v>105035</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>89812</v>
+        <v>95307</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>108683</v>
+        <v>114199</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7111008730915757</v>
+        <v>0.7047584897491944</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6413058046168201</v>
+        <v>0.6394838343743535</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.7760538520639358</v>
+        <v>0.7662484327107075</v>
       </c>
     </row>
     <row r="15">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4198,16 +4198,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4231,67 +4231,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>66080</v>
+        <v>71481</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>54849</v>
+        <v>60288</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>78050</v>
+        <v>84451</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.2797420285860966</v>
+        <v>0.2874848544914089</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.2321959483809797</v>
+        <v>0.2424683607083414</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.3304118024216539</v>
+        <v>0.339650530879622</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>187419</v>
+        <v>198765</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>167434</v>
+        <v>179250</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>208024</v>
+        <v>218676</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.3525997894573501</v>
+        <v>0.3558486175747382</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.3150023636177863</v>
+        <v>0.3209115726201317</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.3913647415747844</v>
+        <v>0.3914969242414433</v>
       </c>
     </row>
     <row r="17">
@@ -4302,67 +4302,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>173977</v>
+        <v>182639</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>158241</v>
+        <v>164852</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>189114</v>
+        <v>198087</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.589122160890129</v>
+        <v>0.5893051957098844</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5358390783859908</v>
+        <v>0.53191412887179</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6403797198228557</v>
+        <v>0.6391501775708668</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>170139</v>
+        <v>177161</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>158169</v>
+        <v>164191</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>181370</v>
+        <v>188354</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7202579714139035</v>
+        <v>0.7125151455085911</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.6695881975783458</v>
+        <v>0.6603494691203782</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.7678040516190201</v>
+        <v>0.7575316392916587</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>344115</v>
+        <v>359800</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>323510</v>
+        <v>339889</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>364100</v>
+        <v>379315</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.6474002105426498</v>
+        <v>0.6441513824252617</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.6086352584252156</v>
+        <v>0.6085030757585567</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.6849976363822137</v>
+        <v>0.6790884273798686</v>
       </c>
     </row>
     <row r="18">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -4394,16 +4394,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -4415,16 +4415,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
